--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>177</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>78</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>108</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>213</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>345</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>332</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>108</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>261</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>244</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>283</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">

--- a/output/glo-pl.xlsx
+++ b/output/glo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
